--- a/artfynd/A 33208-2020 artfynd.xlsx
+++ b/artfynd/A 33208-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118481013</v>
+        <v>118481173</v>
       </c>
       <c r="B2" t="n">
-        <v>57290</v>
+        <v>90522</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585433</v>
+        <v>585471</v>
       </c>
       <c r="R2" t="n">
-        <v>7060346</v>
+        <v>7060312</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118481330</v>
+        <v>118480312</v>
       </c>
       <c r="B3" t="n">
-        <v>58105</v>
+        <v>82263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,47 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585518</v>
+        <v>585790</v>
       </c>
       <c r="R3" t="n">
-        <v>7060228</v>
+        <v>7060116</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118480911</v>
+        <v>118480270</v>
       </c>
       <c r="B4" t="n">
-        <v>97763</v>
+        <v>57290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,41 +901,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585467</v>
+        <v>585825</v>
       </c>
       <c r="R4" t="n">
-        <v>7060317</v>
+        <v>7060103</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,9 +967,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,22 +994,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118480312</v>
+        <v>118481322</v>
       </c>
       <c r="B5" t="n">
-        <v>82263</v>
+        <v>97750</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,25 +1018,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>220093</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,13 +1046,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585790</v>
+        <v>585529</v>
       </c>
       <c r="R5" t="n">
-        <v>7060116</v>
+        <v>7060226</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,19 +1079,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,22 +1096,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118481173</v>
+        <v>118481119</v>
       </c>
       <c r="B6" t="n">
-        <v>90522</v>
+        <v>90504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,21 +1124,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,7 +1151,7 @@
         <v>585471</v>
       </c>
       <c r="R6" t="n">
-        <v>7060312</v>
+        <v>7060301</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1219,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118480885</v>
+        <v>118480911</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
+        <v>97763</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,46 +1222,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585514</v>
+        <v>585467</v>
       </c>
       <c r="R7" t="n">
-        <v>7060272</v>
+        <v>7060317</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,19 +1283,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,22 +1300,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118481322</v>
+        <v>118481330</v>
       </c>
       <c r="B8" t="n">
-        <v>97750</v>
+        <v>58105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,37 +1328,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220093</v>
+        <v>208245</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585529</v>
+        <v>585518</v>
       </c>
       <c r="R8" t="n">
-        <v>7060226</v>
+        <v>7060228</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1409,9 +1394,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,22 +1421,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118481119</v>
+        <v>118481013</v>
       </c>
       <c r="B9" t="n">
-        <v>90504</v>
+        <v>57290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,34 +1449,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585471</v>
+        <v>585433</v>
       </c>
       <c r="R9" t="n">
-        <v>7060301</v>
+        <v>7060346</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1540,7 +1540,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118480270</v>
+        <v>118480885</v>
       </c>
       <c r="B10" t="n">
         <v>57290</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585825</v>
+        <v>585514</v>
       </c>
       <c r="R10" t="n">
-        <v>7060103</v>
+        <v>7060272</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 33208-2020 artfynd.xlsx
+++ b/artfynd/A 33208-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118481173</v>
+        <v>118481031</v>
       </c>
       <c r="B2" t="n">
-        <v>90522</v>
+        <v>57290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585471</v>
+        <v>585433</v>
       </c>
       <c r="R2" t="n">
-        <v>7060312</v>
+        <v>7060346</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118480270</v>
+        <v>118481173</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
+        <v>90522</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,42 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585825</v>
+        <v>585471</v>
       </c>
       <c r="R4" t="n">
-        <v>7060103</v>
+        <v>7060312</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,19 +967,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118481322</v>
+        <v>118480885</v>
       </c>
       <c r="B5" t="n">
-        <v>97750</v>
+        <v>57290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,41 +1008,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585529</v>
+        <v>585514</v>
       </c>
       <c r="R5" t="n">
-        <v>7060226</v>
+        <v>7060272</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,9 +1074,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,22 +1101,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118481119</v>
+        <v>118480270</v>
       </c>
       <c r="B6" t="n">
-        <v>90504</v>
+        <v>57290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,37 +1129,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585471</v>
+        <v>585825</v>
       </c>
       <c r="R6" t="n">
-        <v>7060301</v>
+        <v>7060103</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,9 +1191,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,22 +1218,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118480911</v>
+        <v>118481330</v>
       </c>
       <c r="B7" t="n">
-        <v>97763</v>
+        <v>58105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,37 +1246,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>208245</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585467</v>
+        <v>585518</v>
       </c>
       <c r="R7" t="n">
-        <v>7060317</v>
+        <v>7060228</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,9 +1312,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,22 +1339,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118481330</v>
+        <v>118481119</v>
       </c>
       <c r="B8" t="n">
-        <v>58105</v>
+        <v>90504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,50 +1363,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208245</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585518</v>
+        <v>585471</v>
       </c>
       <c r="R8" t="n">
-        <v>7060228</v>
+        <v>7060301</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,19 +1424,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,22 +1441,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118481013</v>
+        <v>118480911</v>
       </c>
       <c r="B9" t="n">
-        <v>57290</v>
+        <v>97763</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,43 +1465,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585433</v>
+        <v>585467</v>
       </c>
       <c r="R9" t="n">
-        <v>7060346</v>
+        <v>7060317</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1540,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118480885</v>
+        <v>118481322</v>
       </c>
       <c r="B10" t="n">
-        <v>57290</v>
+        <v>97750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,46 +1567,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585514</v>
+        <v>585529</v>
       </c>
       <c r="R10" t="n">
-        <v>7060272</v>
+        <v>7060226</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1618,19 +1628,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,12 +1645,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 33208-2020 artfynd.xlsx
+++ b/artfynd/A 33208-2020 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118480312</v>
+        <v>118480911</v>
       </c>
       <c r="B3" t="n">
-        <v>82263</v>
+        <v>97770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585790</v>
+        <v>585467</v>
       </c>
       <c r="R3" t="n">
-        <v>7060116</v>
+        <v>7060317</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,19 +855,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118481173</v>
+        <v>118480312</v>
       </c>
       <c r="B4" t="n">
-        <v>90522</v>
+        <v>82270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585471</v>
+        <v>585790</v>
       </c>
       <c r="R4" t="n">
-        <v>7060312</v>
+        <v>7060116</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,9 +957,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118480885</v>
+        <v>118481173</v>
       </c>
       <c r="B5" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,42 +1012,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585514</v>
+        <v>585471</v>
       </c>
       <c r="R5" t="n">
-        <v>7060272</v>
+        <v>7060312</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,19 +1069,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,22 +1086,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118480270</v>
+        <v>118481322</v>
       </c>
       <c r="B6" t="n">
-        <v>57290</v>
+        <v>97757</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,46 +1110,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585825</v>
+        <v>585529</v>
       </c>
       <c r="R6" t="n">
-        <v>7060103</v>
+        <v>7060226</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,19 +1171,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,22 +1188,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118481330</v>
+        <v>118480885</v>
       </c>
       <c r="B7" t="n">
-        <v>58105</v>
+        <v>57290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,20 +1212,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208245</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1263,14 +1233,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1279,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585518</v>
+        <v>585514</v>
       </c>
       <c r="R7" t="n">
-        <v>7060228</v>
+        <v>7060272</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118481119</v>
+        <v>118480270</v>
       </c>
       <c r="B8" t="n">
-        <v>90504</v>
+        <v>57290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,37 +1333,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585471</v>
+        <v>585825</v>
       </c>
       <c r="R8" t="n">
-        <v>7060301</v>
+        <v>7060103</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,9 +1395,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,22 +1422,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118480911</v>
+        <v>118481119</v>
       </c>
       <c r="B9" t="n">
-        <v>97763</v>
+        <v>90511</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,25 +1446,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585467</v>
+        <v>585471</v>
       </c>
       <c r="R9" t="n">
-        <v>7060317</v>
+        <v>7060301</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1555,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118481322</v>
+        <v>118481330</v>
       </c>
       <c r="B10" t="n">
-        <v>97750</v>
+        <v>58105</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,37 +1552,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220093</v>
+        <v>208245</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585529</v>
+        <v>585518</v>
       </c>
       <c r="R10" t="n">
-        <v>7060226</v>
+        <v>7060228</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,9 +1618,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,12 +1645,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 33208-2020 artfynd.xlsx
+++ b/artfynd/A 33208-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118481031</v>
+        <v>118480885</v>
       </c>
       <c r="B2" t="n">
         <v>57290</v>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585433</v>
+        <v>585514</v>
       </c>
       <c r="R2" t="n">
-        <v>7060346</v>
+        <v>7060272</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,9 +753,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118480911</v>
+        <v>118480270</v>
       </c>
       <c r="B3" t="n">
-        <v>97770</v>
+        <v>57290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,41 +804,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585467</v>
+        <v>585825</v>
       </c>
       <c r="R3" t="n">
-        <v>7060317</v>
+        <v>7060103</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,9 +870,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118480312</v>
+        <v>118480911</v>
       </c>
       <c r="B4" t="n">
-        <v>82270</v>
+        <v>97770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585790</v>
+        <v>585467</v>
       </c>
       <c r="R4" t="n">
-        <v>7060116</v>
+        <v>7060317</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,19 +982,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118481173</v>
+        <v>118480312</v>
       </c>
       <c r="B5" t="n">
-        <v>90529</v>
+        <v>82270</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585471</v>
+        <v>585790</v>
       </c>
       <c r="R5" t="n">
-        <v>7060312</v>
+        <v>7060116</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,9 +1084,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118481322</v>
+        <v>118481173</v>
       </c>
       <c r="B6" t="n">
-        <v>97757</v>
+        <v>90529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220093</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585529</v>
+        <v>585471</v>
       </c>
       <c r="R6" t="n">
-        <v>7060226</v>
+        <v>7060312</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1200,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118480885</v>
+        <v>118481322</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
+        <v>97757</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,46 +1237,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585514</v>
+        <v>585529</v>
       </c>
       <c r="R7" t="n">
-        <v>7060272</v>
+        <v>7060226</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1278,19 +1298,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,19 +1315,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118480270</v>
+        <v>118481013</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1353,7 +1363,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1362,13 +1372,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585825</v>
+        <v>585433</v>
       </c>
       <c r="R8" t="n">
-        <v>7060103</v>
+        <v>7060346</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1395,19 +1405,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,22 +1422,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118481119</v>
+        <v>118481330</v>
       </c>
       <c r="B9" t="n">
-        <v>90511</v>
+        <v>58105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,41 +1446,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>208245</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585471</v>
+        <v>585518</v>
       </c>
       <c r="R9" t="n">
-        <v>7060301</v>
+        <v>7060228</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,9 +1516,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,22 +1543,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118481330</v>
+        <v>118481119</v>
       </c>
       <c r="B10" t="n">
-        <v>58105</v>
+        <v>90511</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,50 +1567,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208245</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585518</v>
+        <v>585471</v>
       </c>
       <c r="R10" t="n">
-        <v>7060228</v>
+        <v>7060301</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1618,19 +1628,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,12 +1645,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
